--- a/data/raw/benv_exports/leptospirosi_2026_italia.xlsx
+++ b/data/raw/benv_exports/leptospirosi_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>82822</v>
+        <v>83713</v>
       </c>
       <c r="B2" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -423,13 +423,13 @@
         <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>14/01/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>12/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>15/01/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -438,18 +438,18 @@
         <v>CANE</v>
       </c>
       <c r="I2" t="str">
-        <v>BORGOSATOLLO</v>
+        <v>VICENZA</v>
       </c>
       <c r="J2" t="str">
-        <v>BS</v>
+        <v>VI</v>
       </c>
       <c r="K2" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>85201</v>
+        <v>83531</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -458,33 +458,33 @@
         <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>06/07/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>18/06/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>07/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>CANE</v>
+        <v>CAVALLO</v>
       </c>
       <c r="I3" t="str">
-        <v>GAVORRANO</v>
+        <v>CIVITA D\'ANTINO</v>
       </c>
       <c r="J3" t="str">
-        <v>GR</v>
+        <v>AQ</v>
       </c>
       <c r="K3" t="str">
-        <v>TOSCANA</v>
+        <v>ABRUZZO</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>83412</v>
+        <v>84354</v>
       </c>
       <c r="B4" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -493,33 +493,33 @@
         <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>19/02/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>19/02/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>06/05/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>CAVALLO</v>
+        <v>CANE</v>
       </c>
       <c r="I4" t="str">
-        <v>POSTA</v>
+        <v>SAURIS</v>
       </c>
       <c r="J4" t="str">
-        <v>RI</v>
+        <v>UD</v>
       </c>
       <c r="K4" t="str">
-        <v>LAZIO</v>
+        <v>FRIULI VENEZIA GIULIA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>83192</v>
+        <v>84182</v>
       </c>
       <c r="B5" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -528,25 +528,25 @@
         <v>E</v>
       </c>
       <c r="D5" t="str">
-        <v>04/02/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>02/02/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>29/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>BOVINO</v>
+        <v>CAVALLO</v>
       </c>
       <c r="I5" t="str">
-        <v>SORIANO NEL CIMINO</v>
+        <v>ROCCA PRIORA</v>
       </c>
       <c r="J5" t="str">
-        <v>VT</v>
+        <v>RM</v>
       </c>
       <c r="K5" t="str">
         <v>LAZIO</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>83592</v>
+        <v>82822</v>
       </c>
       <c r="B6" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -563,13 +563,13 @@
         <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>21/02/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>20/02/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>04/03/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -578,18 +578,18 @@
         <v>CANE</v>
       </c>
       <c r="I6" t="str">
-        <v>ARCUGNANO</v>
+        <v>BORGOSATOLLO</v>
       </c>
       <c r="J6" t="str">
-        <v>VI</v>
+        <v>BS</v>
       </c>
       <c r="K6" t="str">
-        <v>VENETO</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>84549</v>
+        <v>85064</v>
       </c>
       <c r="B7" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -598,48 +598,48 @@
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>11/05/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>10/02/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>11/06/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>CANE</v>
+        <v>CANIDI</v>
       </c>
       <c r="I7" t="str">
-        <v>PIOVE DI SACCO</v>
+        <v>CASCINA</v>
       </c>
       <c r="J7" t="str">
-        <v>PD</v>
+        <v>PI</v>
       </c>
       <c r="K7" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>84502</v>
+        <v>85201</v>
       </c>
       <c r="B8" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C8" t="str">
         <v>E</v>
       </c>
       <c r="D8" t="str">
-        <v>29/04/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>24/04/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>18/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -648,18 +648,18 @@
         <v>CANE</v>
       </c>
       <c r="I8" t="str">
-        <v>SAN PIETRO IN CARIANO</v>
+        <v>GAVORRANO</v>
       </c>
       <c r="J8" t="str">
-        <v>VR</v>
+        <v>GR</v>
       </c>
       <c r="K8" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>83168</v>
+        <v>83412</v>
       </c>
       <c r="B9" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -668,68 +668,68 @@
         <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>15/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>15/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>30/01/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>CANE</v>
+        <v>CAVALLO</v>
       </c>
       <c r="I9" t="str">
-        <v>CASSACCO</v>
+        <v>POSTA</v>
       </c>
       <c r="J9" t="str">
-        <v>UD</v>
+        <v>RI</v>
       </c>
       <c r="K9" t="str">
-        <v>FRIULI VENEZIA GIULIA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>83713</v>
+        <v>84299</v>
       </c>
       <c r="B10" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C10" t="str">
         <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>11/03/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>05/03/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>12/03/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>CANE</v>
+        <v>BOVINO</v>
       </c>
       <c r="I10" t="str">
-        <v>VICENZA</v>
+        <v>AIELLO DEL FRIULI</v>
       </c>
       <c r="J10" t="str">
-        <v>VI</v>
+        <v>UD</v>
       </c>
       <c r="K10" t="str">
-        <v>VENETO</v>
+        <v>FRIULI VENEZIA GIULIA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>84182</v>
+        <v>83192</v>
       </c>
       <c r="B11" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -738,25 +738,25 @@
         <v>E</v>
       </c>
       <c r="D11" t="str">
-        <v>09/04/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>09/04/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>04/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>CAVALLO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I11" t="str">
-        <v>ROCCA PRIORA</v>
+        <v>SORIANO NEL CIMINO</v>
       </c>
       <c r="J11" t="str">
-        <v>RM</v>
+        <v>VT</v>
       </c>
       <c r="K11" t="str">
         <v>LAZIO</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>84354</v>
+        <v>83592</v>
       </c>
       <c r="B12" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -773,13 +773,13 @@
         <v>E</v>
       </c>
       <c r="D12" t="str">
-        <v>10/04/2026</v>
+        <v>21/02/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>08/04/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>14/04/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -788,33 +788,33 @@
         <v>CANE</v>
       </c>
       <c r="I12" t="str">
-        <v>SAURIS</v>
+        <v>ARCUGNANO</v>
       </c>
       <c r="J12" t="str">
-        <v>UD</v>
+        <v>VI</v>
       </c>
       <c r="K12" t="str">
-        <v>FRIULI VENEZIA GIULIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>85382</v>
+        <v>84549</v>
       </c>
       <c r="B13" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C13" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D13" t="str">
-        <v>29/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>28/05/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="F13" t="str">
-        <v>-</v>
+        <v>11/06/2026</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -823,158 +823,158 @@
         <v>CANE</v>
       </c>
       <c r="I13" t="str">
-        <v>BRESCIA</v>
+        <v>PIOVE DI SACCO</v>
       </c>
       <c r="J13" t="str">
-        <v>BS</v>
+        <v>PD</v>
       </c>
       <c r="K13" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>83531</v>
+        <v>85329</v>
       </c>
       <c r="B14" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C14" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D14" t="str">
-        <v>02/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>02/02/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>-</v>
+        <v>25/07/2026</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>CAVALLO</v>
+        <v>CANE</v>
       </c>
       <c r="I14" t="str">
-        <v>CIVITA D\'ANTINO</v>
+        <v>SORGA\'</v>
       </c>
       <c r="J14" t="str">
-        <v>AQ</v>
+        <v>VR</v>
       </c>
       <c r="K14" t="str">
-        <v>ABRUZZO</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>84299</v>
+        <v>84502</v>
       </c>
       <c r="B15" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C15" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D15" t="str">
+        <v>29/04/2026</v>
+      </c>
+      <c r="E15" t="str">
         <v>24/04/2026</v>
       </c>
-      <c r="E15" t="str">
-        <v>21/04/2026</v>
-      </c>
       <c r="F15" t="str">
-        <v>-</v>
+        <v>18/06/2026</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>BOVINO</v>
+        <v>CANE</v>
       </c>
       <c r="I15" t="str">
-        <v>AIELLO DEL FRIULI</v>
+        <v>SAN PIETRO IN CARIANO</v>
       </c>
       <c r="J15" t="str">
-        <v>UD</v>
+        <v>VR</v>
       </c>
       <c r="K15" t="str">
-        <v>FRIULI VENEZIA GIULIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>85064</v>
+        <v>85382</v>
       </c>
       <c r="B16" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C16" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D16" t="str">
-        <v>08/06/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>21/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="F16" t="str">
-        <v>-</v>
+        <v>20/07/2026</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>CANIDI</v>
+        <v>CANE</v>
       </c>
       <c r="I16" t="str">
-        <v>CASCINA</v>
+        <v>BRESCIA</v>
       </c>
       <c r="J16" t="str">
-        <v>PI</v>
+        <v>BS</v>
       </c>
       <c r="K16" t="str">
-        <v>TOSCANA</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>83865</v>
+        <v>83168</v>
       </c>
       <c r="B17" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C17" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D17" t="str">
-        <v>19/03/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>19/03/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="F17" t="str">
-        <v>-</v>
+        <v>30/01/2026</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>SUINO</v>
+        <v>CANE</v>
       </c>
       <c r="I17" t="str">
-        <v>MEANA SARDO</v>
+        <v>CASSACCO</v>
       </c>
       <c r="J17" t="str">
-        <v>NU</v>
+        <v>UD</v>
       </c>
       <c r="K17" t="str">
-        <v>SARDEGNA</v>
+        <v>FRIULI VENEZIA GIULIA</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>85465</v>
+        <v>85736</v>
       </c>
       <c r="B18" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -983,10 +983,10 @@
         <v>C</v>
       </c>
       <c r="D18" t="str">
-        <v>25/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="E18" t="str">
-        <v>22/06/2026</v>
+        <v>19/07/2026</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -995,21 +995,21 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>CANIDI</v>
+        <v>CANE</v>
       </c>
       <c r="I18" t="str">
-        <v>SANTORSO</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J18" t="str">
-        <v>VI</v>
+        <v>GR</v>
       </c>
       <c r="K18" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>85329</v>
+        <v>85642</v>
       </c>
       <c r="B19" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -1018,10 +1018,10 @@
         <v>C</v>
       </c>
       <c r="D19" t="str">
-        <v>19/06/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E19" t="str">
-        <v>15/06/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
@@ -1030,21 +1030,91 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>CANE</v>
+        <v>BOVINO</v>
       </c>
       <c r="I19" t="str">
-        <v>SORGA\'</v>
+        <v>SORIANO NEL CIMINO</v>
       </c>
       <c r="J19" t="str">
-        <v>VR</v>
+        <v>VT</v>
       </c>
       <c r="K19" t="str">
+        <v>LAZIO</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>83865</v>
+      </c>
+      <c r="B20" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C20" t="str">
+        <v>C</v>
+      </c>
+      <c r="D20" t="str">
+        <v>19/03/2026</v>
+      </c>
+      <c r="E20" t="str">
+        <v>19/03/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>-</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>SUINO</v>
+      </c>
+      <c r="I20" t="str">
+        <v>MEANA SARDO</v>
+      </c>
+      <c r="J20" t="str">
+        <v>NU</v>
+      </c>
+      <c r="K20" t="str">
+        <v>SARDEGNA</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>85465</v>
+      </c>
+      <c r="B21" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C21" t="str">
+        <v>C</v>
+      </c>
+      <c r="D21" t="str">
+        <v>25/06/2026</v>
+      </c>
+      <c r="E21" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>-</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>CANIDI</v>
+      </c>
+      <c r="I21" t="str">
+        <v>SANTORSO</v>
+      </c>
+      <c r="J21" t="str">
+        <v>VI</v>
+      </c>
+      <c r="K21" t="str">
         <v>VENETO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
   </ignoredErrors>
 </worksheet>
 </file>